--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.079457722374616</v>
+        <v>0.6629118798858751</v>
       </c>
       <c r="D2" t="n">
-        <v>39.55982466269743</v>
+        <v>6.428471507688332</v>
       </c>
       <c r="E2" t="n">
-        <v>12.21809894482608</v>
+        <v>1.985441078534237</v>
       </c>
       <c r="F2" t="n">
-        <v>12.50620975209438</v>
+        <v>2.032259084715337</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.94114416171895</v>
+        <v>1.77793592627933</v>
       </c>
       <c r="D3" t="n">
-        <v>12.04119533905555</v>
+        <v>1.956694242596527</v>
       </c>
       <c r="E3" t="n">
-        <v>12.21809894482608</v>
+        <v>1.985441078534237</v>
       </c>
       <c r="F3" t="n">
-        <v>12.50620975209438</v>
+        <v>2.032259084715337</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.0992067527741</v>
+        <v>3.103621097325791</v>
       </c>
       <c r="D4" t="n">
-        <v>19.35524380634989</v>
+        <v>3.145227118531858</v>
       </c>
       <c r="E4" t="n">
-        <v>12.21809894482608</v>
+        <v>1.985441078534237</v>
       </c>
       <c r="F4" t="n">
-        <v>12.50620975209438</v>
+        <v>2.032259084715337</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.192554462661192</v>
+        <v>0.6812901001824437</v>
       </c>
       <c r="D5" t="n">
-        <v>8.286017441456194</v>
+        <v>1.346477834236631</v>
       </c>
       <c r="E5" t="n">
-        <v>12.21809894482608</v>
+        <v>1.985441078534237</v>
       </c>
       <c r="F5" t="n">
-        <v>12.50620975209438</v>
+        <v>2.032259084715337</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.673456732085489</v>
+        <v>0.5969367189638919</v>
       </c>
       <c r="D6" t="n">
-        <v>15.24392169115536</v>
+        <v>2.477137274812747</v>
       </c>
       <c r="E6" t="n">
-        <v>12.21809894482608</v>
+        <v>1.985441078534237</v>
       </c>
       <c r="F6" t="n">
-        <v>12.50620975209438</v>
+        <v>2.032259084715337</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.71032874108566</v>
+        <v>6.12792842042642</v>
       </c>
       <c r="D7" t="n">
-        <v>39.04656497894951</v>
+        <v>6.345066809079296</v>
       </c>
       <c r="E7" t="n">
-        <v>12.21809894482608</v>
+        <v>1.985441078534237</v>
       </c>
       <c r="F7" t="n">
-        <v>12.50620975209438</v>
+        <v>2.032259084715337</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
